--- a/reference_files/OilTariffs_Sample _Results.xlsx
+++ b/reference_files/OilTariffs_Sample _Results.xlsx
@@ -9,11 +9,10 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -34,10 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
-  <si>
-    <t>PipelineName</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="29">
   <si>
     <t>Tallgrass Pony Express Pipeline</t>
   </si>
@@ -45,26 +41,12 @@
     <t>PointOfOrigin</t>
   </si>
   <si>
-    <t>Guernsey PXP
-Located in Platte
-County, WY</t>
-  </si>
-  <si>
     <t>PointOfDestination</t>
   </si>
   <si>
-    <t>Pawnee
-Located in
-Weld
-County, CO</t>
-  </si>
-  <si>
     <t>LiquidTariffNumber</t>
   </si>
   <si>
-    <t>EffectiveDate</t>
-  </si>
-  <si>
     <t>TariffStatus</t>
   </si>
   <si>
@@ -80,135 +62,80 @@
     <t>BPDMax</t>
   </si>
   <si>
-    <t>AcreageDedicationMinAcres</t>
-  </si>
-  <si>
-    <t>AcreageDedicationMaxAcres</t>
-  </si>
-  <si>
     <t>LiquidRateCentsPerBbl</t>
   </si>
   <si>
-    <t>SurchargeCentsPerBbl</t>
-  </si>
-  <si>
     <t>LiquidFuelType</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Augusta
-Located in
-Butler County,
-KS (El Dorado)2</t>
-  </si>
-  <si>
-    <t>Crude (Default)</t>
-  </si>
-  <si>
-    <t>EndDate</t>
-  </si>
-  <si>
     <t>February 28, 2026</t>
   </si>
   <si>
+    <t>RateTier</t>
+  </si>
+  <si>
+    <t>December 1, 2025</t>
+  </si>
+  <si>
+    <t>Pipeline Name</t>
+  </si>
+  <si>
+    <t>Effective Date</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>Page</t>
+  </si>
+  <si>
+    <t>Page 5</t>
+  </si>
+  <si>
     <t>Guernsey
-Located in
-Platte County,
+Located in 
+Platte County, 
 WY</t>
   </si>
   <si>
-    <t>Augusta Located
-in Butler County,
+    <t>Augusta Located 
+in Butler County, 
 KS2</t>
   </si>
   <si>
-    <t>Rate Tier 1</t>
-  </si>
-  <si>
-    <t>Rate Tier 2</t>
-  </si>
-  <si>
-    <t>Platteville Located in Weld County,
+    <t xml:space="preserve"> Rate Tier 1</t>
+  </si>
+  <si>
+    <t>TEMPORARY VOLUME INCENTIVE RATES</t>
+  </si>
+  <si>
+    <t>Curde</t>
+  </si>
+  <si>
+    <t>McPherson 
+Located in 
+McPherson 
+County, KS2</t>
+  </si>
+  <si>
+    <t>P66 Ponca City 
+Located in Kay 
+County, OK</t>
+  </si>
+  <si>
+    <t>Various Cushing 
+Destinations 
+Located in Payne 
+County, OK3</t>
+  </si>
+  <si>
+    <t>Sterling
+Located in 
+Logan County, 
 CO</t>
   </si>
   <si>
-    <t>Sterling Located in Logan County,
-CO</t>
-  </si>
-  <si>
-    <t>RateTier</t>
-  </si>
-  <si>
-    <t>NON-CONTRACT LINE FILL RETURN RATES</t>
-  </si>
-  <si>
-    <t>NON-CONTRACT RATES
-TEMPORARY VOLUME INCENTIVE RATES</t>
-  </si>
-  <si>
-    <t>NON-CONTRACT TRANSPORTATION RATES</t>
-  </si>
-  <si>
-    <t>NON-CONTRACT RATES
-TEMPORARY INCENTIVE RATES
-FOR AGB SEGREGATED BATCHES</t>
-  </si>
-  <si>
-    <t>December 1, 2025</t>
-  </si>
-  <si>
-    <t>02-28-2026</t>
-  </si>
-  <si>
-    <t>Effective (Default)</t>
-  </si>
-  <si>
-    <t>Guernsey, Wyoming</t>
-  </si>
-  <si>
-    <t>Augusta Located in Butler
-County, KS
-(El Dorado)</t>
-  </si>
-  <si>
-    <t>Augusta Blend Incentive Rate</t>
-  </si>
-  <si>
-    <t>Light Incentive Rate</t>
-  </si>
-  <si>
-    <t>CONTRACT VOLUME INCENTIVE RATES</t>
-  </si>
-  <si>
-    <t>Incentive
-Rate</t>
-  </si>
-  <si>
-    <t>Sterling,
-CO</t>
-  </si>
-  <si>
-    <t>Various Cushing
-Destinations located in
-Payne County, OK</t>
-  </si>
-  <si>
-    <t>April 1, 2025</t>
-  </si>
-  <si>
-    <t>May 31,
-2025</t>
-  </si>
-  <si>
-    <t>Pipeline Name</t>
-  </si>
-  <si>
-    <t>Effective Date</t>
-  </si>
-  <si>
-    <t>End Date</t>
+    <t xml:space="preserve"> Rate Tier 2</t>
   </si>
 </sst>
 </file>
@@ -244,12 +171,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -565,325 +491,359 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>17</v>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>12999</v>
+      </c>
+      <c r="N2">
+        <v>515.26</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" t="s">
+    <row r="3" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
         <v>18</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
-        <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
       <c r="I3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3">
-        <v>282.70999999999998</v>
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>12999</v>
+      </c>
+      <c r="N3">
+        <v>515.26</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>12999</v>
+      </c>
+      <c r="N4">
+        <v>515.26</v>
+      </c>
+      <c r="O4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>12999</v>
+      </c>
+      <c r="N5">
+        <v>518.32000000000005</v>
+      </c>
+      <c r="O5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="2">
+        <v>13000</v>
+      </c>
+      <c r="N6">
+        <v>361.07</v>
+      </c>
+      <c r="O6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" t="s">
         <v>22</v>
       </c>
-      <c r="H4" t="s">
+      <c r="L7" s="2">
+        <v>13000</v>
+      </c>
+      <c r="N7">
+        <v>361.07</v>
+      </c>
+      <c r="O7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>12999</v>
-      </c>
-      <c r="O4">
-        <v>515.26</v>
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L8" s="2">
+        <v>13000</v>
+      </c>
+      <c r="N8">
+        <v>361.07</v>
+      </c>
+      <c r="O8" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+    <row r="9" spans="1:15" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="2">
+        <v>13000</v>
+      </c>
+      <c r="N9" s="1">
+        <v>364.13</v>
+      </c>
+      <c r="O9" t="s">
         <v>23</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5">
-        <v>13000</v>
-      </c>
-      <c r="O5">
-        <v>361.07</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6">
-        <v>6000</v>
-      </c>
-      <c r="O6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="45" x14ac:dyDescent="0.25">
-      <c r="I7" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="E8" s="2">
-        <v>45992</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9">
-        <v>387.47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" t="s">
-        <v>41</v>
-      </c>
-      <c r="O10">
-        <v>262.29000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="60" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" s="3">
-        <v>5000</v>
-      </c>
-      <c r="L11" s="3">
-        <v>11999</v>
-      </c>
-      <c r="O11">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="J12">
-        <v>4.3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
